--- a/app/supabase/import/lofty-job-import-template.xlsx
+++ b/app/supabase/import/lofty-job-import-template.xlsx
@@ -813,7 +813,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Row 4 is an example — delete it before sending this back.</t>
+          <t>Row 6 is an example — delete it before sending this back.</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="O6" s="8" t="inlineStr">
         <is>
-          <t>Sales &amp; Acquisition</t>
+          <t>Acquisition &amp; Development</t>
         </is>
       </c>
       <c r="P6" s="8" t="inlineStr">
@@ -7596,7 +7596,7 @@
       <formula1>'Valid values'!$D$4:$D$15</formula1>
     </dataValidation>
     <dataValidation sqref="O6:O306" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a valid value" error="Pick a value from the list. The database rejects anything else in stage." prompt="Choose from the stage list on the Valid values sheet." type="list">
-      <formula1>'Valid values'!$E$4:$E$12</formula1>
+      <formula1>'Valid values'!$E$4:$E$8</formula1>
     </dataValidation>
     <dataValidation sqref="P6:P306" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a valid value" error="Pick a value from the list. The database rejects anything else in job_status." prompt="Choose from the job_status list on the Valid values sheet." type="list">
       <formula1>'Valid values'!$C$4:$C$10</formula1>
@@ -7620,7 +7620,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Sales &amp; Acquisition</t>
+          <t>Acquisition &amp; Development</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Planning &amp; Engineering</t>
+          <t>Pre-construction</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Working Drawings &amp; Contracts</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Handover &amp; Maintenance</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Scheduling &amp; Estimating</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -7891,11 +7891,6 @@
           <t>Selections</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Construction</t>
-        </is>
-      </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Barunga West Council</t>
@@ -7928,11 +7923,6 @@
           <t>Estimating</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Post-construction &amp; Closeout</t>
-        </is>
-      </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Berri Barmera Council</t>
@@ -7960,11 +7950,6 @@
           <t>Construction</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Handover</t>
-        </is>
-      </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
           <t>City of Burnside</t>
@@ -7985,11 +7970,6 @@
       <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Construction Admin</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
